--- a/03_Outputs/Minero_Agroecologica/09_Salud/salud.xlsx
+++ b/03_Outputs/Minero_Agroecologica/09_Salud/salud.xlsx
@@ -906,7 +906,7 @@
         <v>215.642372378245</v>
       </c>
       <c r="F7" s="9">
-        <v>611.865260098188</v>
+        <v>611.865260098189</v>
       </c>
       <c r="G7" s="11">
         <v>397.640260243658</v>
